--- a/html/Børnejounalsystemer_excel.XLSX
+++ b/html/Børnejounalsystemer_excel.XLSX
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CF1D28C-3389-4F1F-A6CE-41818F8CE03F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAC57A3D-49BF-4269-BBBF-EAE8308C5D00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30855" yWindow="1950" windowWidth="21600" windowHeight="11235" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 19-12-2025" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 29-01-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Børnejounalsystemer">'Opdateret d. 19-12-2025'!$A$1:$F$62</definedName>
+    <definedName name="Børnejounalsystemer">'Opdateret d. 29-01-2026'!$A$1:$F$62</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Børnejounalsystemer_excel.XLSX
+++ b/html/Børnejounalsystemer_excel.XLSX
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAC57A3D-49BF-4269-BBBF-EAE8308C5D00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23D77425-ECCB-4B24-8416-C251256EA2EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 29-01-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 02-02-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Børnejounalsystemer">'Opdateret d. 29-01-2026'!$A$1:$F$62</definedName>
+    <definedName name="Børnejounalsystemer">'Opdateret d. 02-02-2026'!$A$1:$F$62</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Børnejounalsystemer_excel.XLSX
+++ b/html/Børnejounalsystemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23D77425-ECCB-4B24-8416-C251256EA2EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D565EF6-AACD-4E7A-B44E-EFA760F49127}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 02-02-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 20-02-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Børnejounalsystemer">'Opdateret d. 02-02-2026'!$A$1:$F$62</definedName>
+    <definedName name="Børnejounalsystemer">'Opdateret d. 20-02-2026'!$A$1:$F$62</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -656,9 +656,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F62"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -678,7 +678,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -692,7 +692,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -706,7 +706,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -720,7 +720,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>15</v>
       </c>
@@ -734,7 +734,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>18</v>
       </c>
@@ -748,7 +748,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>20</v>
       </c>
@@ -762,7 +762,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>22</v>
       </c>
@@ -776,7 +776,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>24</v>
       </c>
@@ -790,7 +790,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>26</v>
       </c>
@@ -804,7 +804,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>28</v>
       </c>
@@ -824,7 +824,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>30</v>
       </c>
@@ -838,7 +838,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>32</v>
       </c>
@@ -855,7 +855,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>34</v>
       </c>
@@ -872,7 +872,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>36</v>
       </c>
@@ -889,7 +889,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>38</v>
       </c>
@@ -903,7 +903,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>40</v>
       </c>
@@ -917,7 +917,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>40</v>
       </c>
@@ -931,7 +931,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>43</v>
       </c>
@@ -945,7 +945,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>45</v>
       </c>
@@ -962,7 +962,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>47</v>
       </c>
@@ -976,7 +976,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>10</v>
       </c>
@@ -990,7 +990,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>12</v>
       </c>
@@ -1004,7 +1004,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>15</v>
       </c>
@@ -1018,7 +1018,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>50</v>
       </c>
@@ -1032,7 +1032,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>18</v>
       </c>
@@ -1046,7 +1046,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>20</v>
       </c>
@@ -1060,7 +1060,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>52</v>
       </c>
@@ -1074,7 +1074,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>22</v>
       </c>
@@ -1088,7 +1088,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>54</v>
       </c>
@@ -1102,7 +1102,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>24</v>
       </c>
@@ -1116,7 +1116,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>26</v>
       </c>
@@ -1130,7 +1130,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>56</v>
       </c>
@@ -1144,7 +1144,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>58</v>
       </c>
@@ -1158,7 +1158,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>60</v>
       </c>
@@ -1172,7 +1172,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>60</v>
       </c>
@@ -1186,7 +1186,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>63</v>
       </c>
@@ -1200,7 +1200,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>65</v>
       </c>
@@ -1214,7 +1214,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>28</v>
       </c>
@@ -1234,7 +1234,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>30</v>
       </c>
@@ -1248,7 +1248,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>67</v>
       </c>
@@ -1265,7 +1265,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>32</v>
       </c>
@@ -1282,7 +1282,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>34</v>
       </c>
@@ -1299,7 +1299,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>36</v>
       </c>
@@ -1316,7 +1316,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>36</v>
       </c>
@@ -1330,7 +1330,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>70</v>
       </c>
@@ -1344,7 +1344,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>72</v>
       </c>
@@ -1358,7 +1358,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>74</v>
       </c>
@@ -1372,7 +1372,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>74</v>
       </c>
@@ -1386,7 +1386,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>77</v>
       </c>
@@ -1400,7 +1400,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>77</v>
       </c>
@@ -1414,7 +1414,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>77</v>
       </c>
@@ -1428,7 +1428,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>81</v>
       </c>
@@ -1442,7 +1442,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>83</v>
       </c>
@@ -1456,7 +1456,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>83</v>
       </c>
@@ -1470,7 +1470,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>86</v>
       </c>
@@ -1490,7 +1490,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>45</v>
       </c>
@@ -1507,7 +1507,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>88</v>
       </c>
@@ -1521,7 +1521,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>90</v>
       </c>
@@ -1535,7 +1535,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>90</v>
       </c>
@@ -1549,7 +1549,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>93</v>
       </c>
@@ -1563,7 +1563,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>95</v>
       </c>

--- a/html/Børnejounalsystemer_excel.XLSX
+++ b/html/Børnejounalsystemer_excel.XLSX
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D565EF6-AACD-4E7A-B44E-EFA760F49127}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B92E25FF-7C1C-42F8-9CFC-CC68957046EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 20-02-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 04-03-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Børnejounalsystemer">'Opdateret d. 20-02-2026'!$A$1:$F$62</definedName>
+    <definedName name="Børnejounalsystemer">'Opdateret d. 04-03-2026'!$A$1:$F$62</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Børnejounalsystemer_excel.XLSX
+++ b/html/Børnejounalsystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B92E25FF-7C1C-42F8-9CFC-CC68957046EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B4C2594-6598-4E05-BEB3-9FBADDF43258}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 04-03-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 06-03-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Børnejounalsystemer">'Opdateret d. 04-03-2026'!$A$1:$F$62</definedName>
+    <definedName name="Børnejounalsystemer">'Opdateret d. 06-03-2026'!$A$1:$F$62</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Børnejounalsystemer_excel.XLSX
+++ b/html/Børnejounalsystemer_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B4C2594-6598-4E05-BEB3-9FBADDF43258}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0B18BC9-FDBD-4125-A252-98BAF552A5B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/Børnejounalsystemer_excel.XLSX
+++ b/html/Børnejounalsystemer_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0B18BC9-FDBD-4125-A252-98BAF552A5B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A95C170-9E85-4181-A375-3DB4DEB13DEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/Børnejounalsystemer_excel.XLSX
+++ b/html/Børnejounalsystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A95C170-9E85-4181-A375-3DB4DEB13DEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5999EF9-AA54-4DF4-8BEA-F04D3FE1AF70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14625" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 06-03-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 09-03-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Børnejounalsystemer">'Opdateret d. 06-03-2026'!$A$1:$F$62</definedName>
+    <definedName name="Børnejounalsystemer">'Opdateret d. 09-03-2026'!$A$1:$F$62</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Børnejounalsystemer_excel.XLSX
+++ b/html/Børnejounalsystemer_excel.XLSX
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5999EF9-AA54-4DF4-8BEA-F04D3FE1AF70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF1EB5F4-7B13-46F4-8227-638E05060B1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14625" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Opdateret d. 09-03-2026" sheetId="1" r:id="rId1"/>

--- a/html/Børnejounalsystemer_excel.XLSX
+++ b/html/Børnejounalsystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF1EB5F4-7B13-46F4-8227-638E05060B1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17EDDF72-9D40-40A4-B4C0-52DC760CC1C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 09-03-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 11-03-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Børnejounalsystemer">'Opdateret d. 09-03-2026'!$A$1:$F$62</definedName>
+    <definedName name="Børnejounalsystemer">'Opdateret d. 11-03-2026'!$A$1:$F$62</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Børnejounalsystemer_excel.XLSX
+++ b/html/Børnejounalsystemer_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17EDDF72-9D40-40A4-B4C0-52DC760CC1C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81806172-13D8-4448-8B79-6DDEE171B653}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/Børnejounalsystemer_excel.XLSX
+++ b/html/Børnejounalsystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81806172-13D8-4448-8B79-6DDEE171B653}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13CBB3C8-288A-4173-A280-CCEA6F29FE76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 11-03-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 20-03-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Børnejounalsystemer">'Opdateret d. 11-03-2026'!$A$1:$F$62</definedName>
+    <definedName name="Børnejounalsystemer">'Opdateret d. 20-03-2026'!$A$1:$F$62</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -40,7 +40,7 @@
     <t>Novax Sundhed (Novax)</t>
   </si>
   <si>
-    <t>TM sund (TM Care)</t>
+    <t>SUND (Confirma Danmark)</t>
   </si>
   <si>
     <t>Acknowledgement</t>

--- a/html/Børnejounalsystemer_excel.XLSX
+++ b/html/Børnejounalsystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13CBB3C8-288A-4173-A280-CCEA6F29FE76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69D0E1E7-CBDA-43B7-ACE0-742C52B20366}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 20-03-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 25-03-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Børnejounalsystemer">'Opdateret d. 20-03-2026'!$A$1:$F$62</definedName>
+    <definedName name="Børnejounalsystemer">'Opdateret d. 25-03-2026'!$A$1:$F$62</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Børnejounalsystemer_excel.XLSX
+++ b/html/Børnejounalsystemer_excel.XLSX
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69D0E1E7-CBDA-43B7-ACE0-742C52B20366}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E470A7E6-A78F-4624-A3A1-248672268DDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="768" yWindow="768" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 25-03-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 08-04-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Børnejounalsystemer">'Opdateret d. 25-03-2026'!$A$1:$F$62</definedName>
+    <definedName name="Børnejounalsystemer">'Opdateret d. 08-04-2026'!$A$1:$F$62</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Børnejounalsystemer_excel.XLSX
+++ b/html/Børnejounalsystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E470A7E6-A78F-4624-A3A1-248672268DDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{666B5D0B-5B78-45F1-86CD-43A3F817B756}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="768" yWindow="768" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 08-04-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 10-04-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Børnejounalsystemer">'Opdateret d. 08-04-2026'!$A$1:$F$62</definedName>
+    <definedName name="Børnejounalsystemer">'Opdateret d. 10-04-2026'!$A$1:$F$62</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Børnejounalsystemer_excel.XLSX
+++ b/html/Børnejounalsystemer_excel.XLSX
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{666B5D0B-5B78-45F1-86CD-43A3F817B756}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D976B99-E796-4D6C-807A-7C7E0E9224A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="768" yWindow="768" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-15045" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Opdateret d. 10-04-2026" sheetId="1" r:id="rId1"/>

--- a/html/Børnejounalsystemer_excel.XLSX
+++ b/html/Børnejounalsystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D976B99-E796-4D6C-807A-7C7E0E9224A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE61E46B-ED61-4630-AF0F-8A043C66F6DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-15045" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 10-04-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 14-04-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Børnejounalsystemer">'Opdateret d. 10-04-2026'!$A$1:$F$62</definedName>
+    <definedName name="Børnejounalsystemer">'Opdateret d. 14-04-2026'!$A$1:$F$62</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Børnejounalsystemer_excel.XLSX
+++ b/html/Børnejounalsystemer_excel.XLSX
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE61E46B-ED61-4630-AF0F-8A043C66F6DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3BFB0ED-B25B-42F5-90A0-DD5BABEAB757}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 14-04-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 24-04-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Børnejounalsystemer">'Opdateret d. 14-04-2026'!$A$1:$F$62</definedName>
+    <definedName name="Børnejounalsystemer">'Opdateret d. 24-04-2026'!$A$1:$F$62</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Børnejounalsystemer_excel.XLSX
+++ b/html/Børnejounalsystemer_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3BFB0ED-B25B-42F5-90A0-DD5BABEAB757}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0DEA062-E4BA-48DF-A4BC-0027241CF3A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/Børnejounalsystemer_excel.XLSX
+++ b/html/Børnejounalsystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0DEA062-E4BA-48DF-A4BC-0027241CF3A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDD893B7-ACBB-4246-892C-31E8100978E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="768" yWindow="768" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 24-04-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 27-04-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Børnejounalsystemer">'Opdateret d. 24-04-2026'!$A$1:$F$62</definedName>
+    <definedName name="Børnejounalsystemer">'Opdateret d. 27-04-2026'!$A$1:$F$62</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -73,7 +73,7 @@
     <t>CareCommunication</t>
   </si>
   <si>
-    <t>CareCommunication (4.0)</t>
+    <t>CareCommunication (5.0)</t>
   </si>
   <si>
     <t>Tester</t>

--- a/html/Børnejounalsystemer_excel.XLSX
+++ b/html/Børnejounalsystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDD893B7-ACBB-4246-892C-31E8100978E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFBDE555-DC8A-4A9D-93F5-E37E0497FB7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="768" yWindow="768" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="384" yWindow="384" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 27-04-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 06-05-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Børnejounalsystemer">'Opdateret d. 27-04-2026'!$A$1:$F$62</definedName>
+    <definedName name="Børnejounalsystemer">'Opdateret d. 06-05-2026'!$A$1:$F$62</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Børnejounalsystemer_excel.XLSX
+++ b/html/Børnejounalsystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFBDE555-DC8A-4A9D-93F5-E37E0497FB7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BEE5663-2589-41B8-92C3-8041E35CDD7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="384" yWindow="384" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 06-05-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 01-06-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Børnejounalsystemer">'Opdateret d. 06-05-2026'!$A$1:$F$62</definedName>
+    <definedName name="Børnejounalsystemer">'Opdateret d. 01-06-2026'!$A$1:$F$62</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Børnejounalsystemer_excel.XLSX
+++ b/html/Børnejounalsystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BEE5663-2589-41B8-92C3-8041E35CDD7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{381F85DA-528D-4BF4-AA48-50E2CD487BC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 01-06-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 02-06-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Børnejounalsystemer">'Opdateret d. 01-06-2026'!$A$1:$F$62</definedName>
+    <definedName name="Børnejounalsystemer">'Opdateret d. 02-06-2026'!$A$1:$F$62</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Børnejounalsystemer_excel.XLSX
+++ b/html/Børnejounalsystemer_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{381F85DA-528D-4BF4-AA48-50E2CD487BC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCB84B67-0964-47E2-A2DA-C8A4C7368578}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/Børnejounalsystemer_excel.XLSX
+++ b/html/Børnejounalsystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCB84B67-0964-47E2-A2DA-C8A4C7368578}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8297924-4FDE-479D-BAFE-64CA3740E0FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 02-06-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 05-06-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Børnejounalsystemer">'Opdateret d. 02-06-2026'!$A$1:$F$62</definedName>
+    <definedName name="Børnejounalsystemer">'Opdateret d. 05-06-2026'!$A$1:$F$62</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Børnejounalsystemer_excel.XLSX
+++ b/html/Børnejounalsystemer_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAC57A3D-49BF-4269-BBBF-EAE8308C5D00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{269840FB-6E70-445F-9E8F-569630C91309}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/Børnejounalsystemer_excel.XLSX
+++ b/html/Børnejounalsystemer_excel.XLSX
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{269840FB-6E70-445F-9E8F-569630C91309}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1034B436-FAEC-46EB-A17B-8E81E63404C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3150" yWindow="3135" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 29-01-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 09-06-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Børnejounalsystemer">'Opdateret d. 29-01-2026'!$A$1:$F$62</definedName>
+    <definedName name="Børnejounalsystemer">'Opdateret d. 09-06-2026'!$A$1:$F$62</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -40,7 +40,7 @@
     <t>Novax Sundhed (Novax)</t>
   </si>
   <si>
-    <t>TM sund (TM Care)</t>
+    <t>SUND (Confirma Danmark)</t>
   </si>
   <si>
     <t>Acknowledgement</t>
@@ -73,7 +73,7 @@
     <t>CareCommunication</t>
   </si>
   <si>
-    <t>CareCommunication (4.0)</t>
+    <t>CareCommunication (5.0)</t>
   </si>
   <si>
     <t>Tester</t>

--- a/html/Børnejounalsystemer_excel.XLSX
+++ b/html/Børnejounalsystemer_excel.XLSX
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1034B436-FAEC-46EB-A17B-8E81E63404C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D4DABC1-6491-42D0-8C65-EE5FF172758E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3150" yWindow="3135" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Opdateret d. 09-06-2026" sheetId="1" r:id="rId1"/>

--- a/html/Børnejounalsystemer_excel.XLSX
+++ b/html/Børnejounalsystemer_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D4DABC1-6491-42D0-8C65-EE5FF172758E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7ADE9EEA-B262-4E95-BF1A-93F60ECC3C53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/Børnejounalsystemer_excel.XLSX
+++ b/html/Børnejounalsystemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7ADE9EEA-B262-4E95-BF1A-93F60ECC3C53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1171CE29-060B-4E05-9299-6B58ADA383D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 09-06-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 15-06-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Børnejounalsystemer">'Opdateret d. 09-06-2026'!$A$1:$F$62</definedName>
+    <definedName name="Børnejounalsystemer">'Opdateret d. 15-06-2026'!$A$1:$F$62</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -656,9 +656,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F62"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -678,7 +678,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -692,7 +692,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -706,7 +706,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -720,7 +720,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>15</v>
       </c>
@@ -734,7 +734,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>18</v>
       </c>
@@ -748,7 +748,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>20</v>
       </c>
@@ -762,7 +762,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>22</v>
       </c>
@@ -776,7 +776,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>24</v>
       </c>
@@ -790,7 +790,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>26</v>
       </c>
@@ -804,7 +804,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>28</v>
       </c>
@@ -824,7 +824,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>30</v>
       </c>
@@ -838,7 +838,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>32</v>
       </c>
@@ -855,7 +855,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>34</v>
       </c>
@@ -872,7 +872,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>36</v>
       </c>
@@ -889,7 +889,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>38</v>
       </c>
@@ -903,7 +903,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>40</v>
       </c>
@@ -917,7 +917,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>40</v>
       </c>
@@ -931,7 +931,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>43</v>
       </c>
@@ -945,7 +945,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>45</v>
       </c>
@@ -962,7 +962,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>47</v>
       </c>
@@ -976,7 +976,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>10</v>
       </c>
@@ -990,7 +990,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>12</v>
       </c>
@@ -1004,7 +1004,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>15</v>
       </c>
@@ -1018,7 +1018,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>50</v>
       </c>
@@ -1032,7 +1032,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>18</v>
       </c>
@@ -1046,7 +1046,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>20</v>
       </c>
@@ -1060,7 +1060,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>52</v>
       </c>
@@ -1074,7 +1074,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>22</v>
       </c>
@@ -1088,7 +1088,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>54</v>
       </c>
@@ -1102,7 +1102,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>24</v>
       </c>
@@ -1116,7 +1116,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>26</v>
       </c>
@@ -1130,7 +1130,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>56</v>
       </c>
@@ -1144,7 +1144,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>58</v>
       </c>
@@ -1158,7 +1158,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>60</v>
       </c>
@@ -1172,7 +1172,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>60</v>
       </c>
@@ -1186,7 +1186,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>63</v>
       </c>
@@ -1200,7 +1200,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>65</v>
       </c>
@@ -1214,7 +1214,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>28</v>
       </c>
@@ -1234,7 +1234,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>30</v>
       </c>
@@ -1248,7 +1248,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>67</v>
       </c>
@@ -1265,7 +1265,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>32</v>
       </c>
@@ -1282,7 +1282,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>34</v>
       </c>
@@ -1299,7 +1299,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>36</v>
       </c>
@@ -1316,7 +1316,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>36</v>
       </c>
@@ -1330,7 +1330,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>70</v>
       </c>
@@ -1344,7 +1344,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>72</v>
       </c>
@@ -1358,7 +1358,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>74</v>
       </c>
@@ -1372,7 +1372,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>74</v>
       </c>
@@ -1386,7 +1386,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>77</v>
       </c>
@@ -1400,7 +1400,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>77</v>
       </c>
@@ -1414,7 +1414,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>77</v>
       </c>
@@ -1428,7 +1428,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>81</v>
       </c>
@@ -1442,7 +1442,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>83</v>
       </c>
@@ -1456,7 +1456,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>83</v>
       </c>
@@ -1470,7 +1470,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>86</v>
       </c>
@@ -1490,7 +1490,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>45</v>
       </c>
@@ -1507,7 +1507,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>88</v>
       </c>
@@ -1521,7 +1521,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>90</v>
       </c>
@@ -1535,7 +1535,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>90</v>
       </c>
@@ -1549,7 +1549,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>93</v>
       </c>
@@ -1563,7 +1563,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>95</v>
       </c>

--- a/html/Børnejounalsystemer_excel.XLSX
+++ b/html/Børnejounalsystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1171CE29-060B-4E05-9299-6B58ADA383D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9247A077-2E60-4FB7-909C-A3FB86563CD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 15-06-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 22-06-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Børnejounalsystemer">'Opdateret d. 15-06-2026'!$A$1:$F$62</definedName>
+    <definedName name="Børnejounalsystemer">'Opdateret d. 22-06-2026'!$A$1:$F$62</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Børnejounalsystemer_excel.XLSX
+++ b/html/Børnejounalsystemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9247A077-2E60-4FB7-909C-A3FB86563CD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B984173D-C3E8-453A-BC97-B46F131E4043}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 22-06-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 23-06-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Børnejounalsystemer">'Opdateret d. 22-06-2026'!$A$1:$F$62</definedName>
+    <definedName name="Børnejounalsystemer">'Opdateret d. 23-06-2026'!$A$1:$F$62</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -656,9 +656,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F62"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -678,7 +678,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -692,7 +692,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -706,7 +706,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -720,7 +720,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>15</v>
       </c>
@@ -734,7 +734,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>18</v>
       </c>
@@ -748,7 +748,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>20</v>
       </c>
@@ -762,7 +762,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>22</v>
       </c>
@@ -776,7 +776,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>24</v>
       </c>
@@ -790,7 +790,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>26</v>
       </c>
@@ -804,7 +804,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>28</v>
       </c>
@@ -824,7 +824,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>30</v>
       </c>
@@ -838,7 +838,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>32</v>
       </c>
@@ -855,7 +855,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>34</v>
       </c>
@@ -872,7 +872,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>36</v>
       </c>
@@ -889,7 +889,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>38</v>
       </c>
@@ -903,7 +903,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>40</v>
       </c>
@@ -917,7 +917,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>40</v>
       </c>
@@ -931,7 +931,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>43</v>
       </c>
@@ -945,7 +945,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>45</v>
       </c>
@@ -962,7 +962,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>47</v>
       </c>
@@ -976,7 +976,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>10</v>
       </c>
@@ -990,7 +990,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>12</v>
       </c>
@@ -1004,7 +1004,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>15</v>
       </c>
@@ -1018,7 +1018,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>50</v>
       </c>
@@ -1032,7 +1032,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>18</v>
       </c>
@@ -1046,7 +1046,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>20</v>
       </c>
@@ -1060,7 +1060,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>52</v>
       </c>
@@ -1074,7 +1074,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>22</v>
       </c>
@@ -1088,7 +1088,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>54</v>
       </c>
@@ -1102,7 +1102,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>24</v>
       </c>
@@ -1116,7 +1116,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>26</v>
       </c>
@@ -1130,7 +1130,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>56</v>
       </c>
@@ -1144,7 +1144,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>58</v>
       </c>
@@ -1158,7 +1158,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>60</v>
       </c>
@@ -1172,7 +1172,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>60</v>
       </c>
@@ -1186,7 +1186,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>63</v>
       </c>
@@ -1200,7 +1200,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>65</v>
       </c>
@@ -1214,7 +1214,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>28</v>
       </c>
@@ -1234,7 +1234,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>30</v>
       </c>
@@ -1248,7 +1248,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>67</v>
       </c>
@@ -1265,7 +1265,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>32</v>
       </c>
@@ -1282,7 +1282,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>34</v>
       </c>
@@ -1299,7 +1299,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>36</v>
       </c>
@@ -1316,7 +1316,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>36</v>
       </c>
@@ -1330,7 +1330,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>70</v>
       </c>
@@ -1344,7 +1344,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>72</v>
       </c>
@@ -1358,7 +1358,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>74</v>
       </c>
@@ -1372,7 +1372,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>74</v>
       </c>
@@ -1386,7 +1386,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>77</v>
       </c>
@@ -1400,7 +1400,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>77</v>
       </c>
@@ -1414,7 +1414,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>77</v>
       </c>
@@ -1428,7 +1428,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>81</v>
       </c>
@@ -1442,7 +1442,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>83</v>
       </c>
@@ -1456,7 +1456,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>83</v>
       </c>
@@ -1470,7 +1470,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>86</v>
       </c>
@@ -1490,7 +1490,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>45</v>
       </c>
@@ -1507,7 +1507,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>88</v>
       </c>
@@ -1521,7 +1521,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>90</v>
       </c>
@@ -1535,7 +1535,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>90</v>
       </c>
@@ -1549,7 +1549,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>93</v>
       </c>
@@ -1563,7 +1563,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>95</v>
       </c>

--- a/html/Børnejounalsystemer_excel.XLSX
+++ b/html/Børnejounalsystemer_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B984173D-C3E8-453A-BC97-B46F131E4043}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4F5686D-7DB1-41A8-9C29-9961AAEBECE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/Børnejounalsystemer_excel.XLSX
+++ b/html/Børnejounalsystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9247A077-2E60-4FB7-909C-A3FB86563CD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2592AF9C-C98B-4B77-8475-064D358AB10E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2304" yWindow="2304" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 22-06-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 23-06-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Børnejounalsystemer">'Opdateret d. 22-06-2026'!$A$1:$F$62</definedName>
+    <definedName name="Børnejounalsystemer">'Opdateret d. 23-06-2026'!$A$1:$F$62</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Børnejounalsystemer_excel.XLSX
+++ b/html/Børnejounalsystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2592AF9C-C98B-4B77-8475-064D358AB10E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCADBFCE-D690-4887-ADCB-00741A036C08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2304" yWindow="2304" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 23-06-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 25-06-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Børnejounalsystemer">'Opdateret d. 23-06-2026'!$A$1:$F$62</definedName>
+    <definedName name="Børnejounalsystemer">'Opdateret d. 25-06-2026'!$A$1:$F$62</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Børnejounalsystemer_excel.XLSX
+++ b/html/Børnejounalsystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCADBFCE-D690-4887-ADCB-00741A036C08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49896E9E-ECE0-4649-9519-7F77E5D88D34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2304" yWindow="2304" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 25-06-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 30-06-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Børnejounalsystemer">'Opdateret d. 25-06-2026'!$A$1:$F$62</definedName>
+    <definedName name="Børnejounalsystemer">'Opdateret d. 30-06-2026'!$A$1:$F$62</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Børnejounalsystemer_excel.XLSX
+++ b/html/Børnejounalsystemer_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49896E9E-ECE0-4649-9519-7F77E5D88D34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F83116C-6A66-490F-B43E-F48A08C18CDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/Børnejounalsystemer_excel.XLSX
+++ b/html/Børnejounalsystemer_excel.XLSX
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F83116C-6A66-490F-B43E-F48A08C18CDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03BE34E1-18FD-4041-AA75-A0DC93A804A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 30-06-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 01-07-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Børnejounalsystemer">'Opdateret d. 30-06-2026'!$A$1:$F$62</definedName>
+    <definedName name="Børnejounalsystemer">'Opdateret d. 01-07-2026'!$A$1:$F$62</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -656,9 +656,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F62"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -678,7 +678,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -692,7 +692,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -706,7 +706,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -720,7 +720,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>15</v>
       </c>
@@ -734,7 +734,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>18</v>
       </c>
@@ -748,7 +748,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>20</v>
       </c>
@@ -762,7 +762,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>22</v>
       </c>
@@ -776,7 +776,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>24</v>
       </c>
@@ -790,7 +790,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>26</v>
       </c>
@@ -804,7 +804,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>28</v>
       </c>
@@ -824,7 +824,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>30</v>
       </c>
@@ -838,7 +838,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>32</v>
       </c>
@@ -855,7 +855,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>34</v>
       </c>
@@ -872,7 +872,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>36</v>
       </c>
@@ -889,7 +889,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>38</v>
       </c>
@@ -903,7 +903,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>40</v>
       </c>
@@ -917,7 +917,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>40</v>
       </c>
@@ -931,7 +931,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>43</v>
       </c>
@@ -945,7 +945,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>45</v>
       </c>
@@ -962,7 +962,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>47</v>
       </c>
@@ -976,7 +976,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>10</v>
       </c>
@@ -990,7 +990,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>12</v>
       </c>
@@ -1004,7 +1004,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>15</v>
       </c>
@@ -1018,7 +1018,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>50</v>
       </c>
@@ -1032,7 +1032,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>18</v>
       </c>
@@ -1046,7 +1046,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>20</v>
       </c>
@@ -1060,7 +1060,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>52</v>
       </c>
@@ -1074,7 +1074,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>22</v>
       </c>
@@ -1088,7 +1088,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>54</v>
       </c>
@@ -1102,7 +1102,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>24</v>
       </c>
@@ -1116,7 +1116,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>26</v>
       </c>
@@ -1130,7 +1130,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>56</v>
       </c>
@@ -1144,7 +1144,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>58</v>
       </c>
@@ -1158,7 +1158,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>60</v>
       </c>
@@ -1172,7 +1172,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>60</v>
       </c>
@@ -1186,7 +1186,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>63</v>
       </c>
@@ -1200,7 +1200,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>65</v>
       </c>
@@ -1214,7 +1214,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>28</v>
       </c>
@@ -1234,7 +1234,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>30</v>
       </c>
@@ -1248,7 +1248,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>67</v>
       </c>
@@ -1265,7 +1265,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>32</v>
       </c>
@@ -1282,7 +1282,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>34</v>
       </c>
@@ -1299,7 +1299,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>36</v>
       </c>
@@ -1316,7 +1316,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>36</v>
       </c>
@@ -1330,7 +1330,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>70</v>
       </c>
@@ -1344,7 +1344,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>72</v>
       </c>
@@ -1358,7 +1358,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>74</v>
       </c>
@@ -1372,7 +1372,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>74</v>
       </c>
@@ -1386,7 +1386,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>77</v>
       </c>
@@ -1400,7 +1400,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>77</v>
       </c>
@@ -1414,7 +1414,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>77</v>
       </c>
@@ -1428,7 +1428,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>81</v>
       </c>
@@ -1442,7 +1442,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>83</v>
       </c>
@@ -1456,7 +1456,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>83</v>
       </c>
@@ -1470,7 +1470,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>86</v>
       </c>
@@ -1490,7 +1490,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>45</v>
       </c>
@@ -1507,7 +1507,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>88</v>
       </c>
@@ -1521,7 +1521,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>90</v>
       </c>
@@ -1535,7 +1535,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>90</v>
       </c>
@@ -1549,7 +1549,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>93</v>
       </c>
@@ -1563,7 +1563,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>95</v>
       </c>
